--- a/out/MLP-S4_repeat_4_000006.xlsx
+++ b/out/MLP-S4_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.905762781659078</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.305762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.305762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004335500349259237</v>
+        <v>-0.0003217451348025352</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5580126668720173</v>
+        <v>0.4141108407685089</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.117081362129436</v>
+        <v>0.8290058003310873</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1288680609038925</v>
+        <v>-0.09563531163542903</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.3181537839982775</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.305762781659078</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.3181537839982775</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.305762781659078</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4282905671293025</v>
+        <v>0.317874030467744</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.291832382128857</v>
+        <v>0.8594633479055712</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.014527996781645</v>
+        <v>2.038512118685154</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2471775704005052</v>
+        <v>0.1644485653896632</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.305762781659078</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.215165378262322</v>
+        <v>1.50669180736866</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4329549564050205</v>
+        <v>0.288047258267752</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.305762781659078</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.834019196562892</v>
+        <v>1.91841868128348</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2371021278781488</v>
+        <v>0.1577451608387375</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.874894879453305</v>
+        <v>1.945613506873808</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09792663180010021</v>
+        <v>0.06515124552584857</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.833397458235803</v>
+        <v>1.918004993962326</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1220076893054998</v>
+        <v>0.08117237060192903</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.305762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.979503623249646</v>
+        <v>2.015210406641441</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07346497957632797</v>
+        <v>0.04887625232955294</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.004342117273686</v>
+        <v>2.031735657840622</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05585313394007747</v>
+        <v>0.03715998910605837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.305762781659078</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.042552013093021</v>
+        <v>2.057157316612956</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02470398649499714</v>
+        <v>0.01643595988750051</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.036057590715974</v>
+        <v>2.052836472861554</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01960153860508638</v>
+        <v>0.0130398794981484</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.050550307793771</v>
+        <v>2.062477793758531</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009718253783466718</v>
+        <v>0.006463827960906852</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.305762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.050371751089294</v>
+        <v>2.06235732047787</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005650486249503828</v>
+        <v>0.003756596564098997</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.051946831408553</v>
+        <v>2.063403677172157</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002822743124751914</v>
+        <v>0.001877252882422313</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.905762781659078</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.051938310677476</v>
+        <v>2.063396333640256</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001392079006917507</v>
+        <v>0.0009235113564492899</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.905762781659078</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.051897945025743</v>
+        <v>2.063367794713835</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008060496250303649</v>
+        <v>0.0005356997500202434</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.905762781659078</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.05211723034811</v>
+        <v>2.06351231826208</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002650683837906009</v>
+        <v>0.0001757895792317245</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.051842886828066</v>
+        <v>2.063327754979218</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001319932599835336</v>
+        <v>8.483164589084172e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.051839402688656</v>
+        <v>2.0633237628238</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.838588390325518e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.05184655010353</v>
+        <v>2.063326927982303</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.055270670444892e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.051839146167925</v>
+        <v>2.063320299989562</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.051842751877116</v>
+        <v>2.063321218225707</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.051835082156022</v>
+        <v>2.063314215934886</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.051831596935714</v>
+        <v>2.063310353859789</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.051827049623529</v>
+        <v>2.063305806547604</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.051827139568179</v>
+        <v>2.063305896492254</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.051826281634594</v>
+        <v>2.063305038558669</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.051826509955628</v>
+        <v>2.063305266879704</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.051825714291417</v>
+        <v>2.063304471215492</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.051825776560789</v>
+        <v>2.063304533484866</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.051825804236067</v>
+        <v>2.063304561160142</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.051825956450089</v>
+        <v>2.063304713374166</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.051825610509128</v>
+        <v>2.063304367433204</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.05182568661614</v>
+        <v>2.063304443540216</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.051825852667801</v>
+        <v>2.063304609591877</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.051826212446401</v>
+        <v>2.063304969370477</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.051826233202859</v>
+        <v>2.063304990126935</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.051826336985147</v>
+        <v>2.063305093909223</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.051826565306182</v>
+        <v>2.063305322230258</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.051826440767436</v>
+        <v>2.063305197691512</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.051826468442713</v>
+        <v>2.063305225366789</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.051826523793267</v>
+        <v>2.063305280717342</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.051826786708397</v>
+        <v>2.063305543632473</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.051826703682567</v>
+        <v>2.063305460606642</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.05182649611799</v>
+        <v>2.063305253042066</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.051826509955628</v>
+        <v>2.063305266879704</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.051826648332013</v>
+        <v>2.063305405256089</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.051826364660424</v>
+        <v>2.0633051215845</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.051826191689944</v>
+        <v>2.063304948614019</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.051826087907655</v>
+        <v>2.063304844831731</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.051826233202859</v>
+        <v>2.063304990126935</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.051826475361532</v>
+        <v>2.063305232285608</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.051826302391051</v>
+        <v>2.063305059315127</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.051826004881824</v>
+        <v>2.0633047618059</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.051825991044185</v>
+        <v>2.063304747968262</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.051825624346766</v>
+        <v>2.063304381270842</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.051825624346766</v>
+        <v>2.063304381270842</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.051825562077393</v>
+        <v>2.063304319001469</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.051825458295105</v>
+        <v>2.063304215219181</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.051825285324624</v>
+        <v>2.0633040422487</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.051825333756359</v>
+        <v>2.063304090680434</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.051824973977759</v>
+        <v>2.063303730901834</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.051824932464843</v>
+        <v>2.063303689388919</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.051824987815397</v>
+        <v>2.063303744739473</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.051825043165951</v>
+        <v>2.063303800090027</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.051825084678867</v>
+        <v>2.063303841602942</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.051824814844916</v>
+        <v>2.063303571768992</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.05182487019547</v>
+        <v>2.063303627119546</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.051825015490674</v>
+        <v>2.06330377241475</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.051824980896578</v>
+        <v>2.063303737820654</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.051824967058939</v>
+        <v>2.063303723983015</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.051825057003589</v>
+        <v>2.063303813927665</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.905762781659078</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.051825375269274</v>
+        <v>2.06330413219335</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.051825195379974</v>
+        <v>2.06330395230405</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.051825236892889</v>
+        <v>2.063303993816965</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.05182505008477</v>
+        <v>2.063303807008846</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.051825119272962</v>
+        <v>2.063303876197038</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.051824918627205</v>
+        <v>2.063303675551281</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.05182496014012</v>
+        <v>2.063303717064196</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.051824987815397</v>
+        <v>2.063303744739473</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000006.xlsx
+++ b/out/MLP-S4_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.905762781659078</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.305762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004335500349259237</v>
+        <v>-0.0003234725534667959</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5580126668720173</v>
+        <v>0.4163341631488183</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.117081362129436</v>
+        <v>0.8334566526871295</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1288680609038925</v>
+        <v>-0.09614876815877423</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.3198619224365773</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.305762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.3198619224365773</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4282905671293025</v>
+        <v>0.3196210123567867</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.291832382128857</v>
+        <v>0.7401277043068341</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.014527996781645</v>
+        <v>1.801350513402749</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2471775704005052</v>
+        <v>0.1416150967164862</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.215165378262322</v>
+        <v>1.343372730344206</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4329549564050205</v>
+        <v>0.2480522724041377</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.834019196562892</v>
+        <v>1.697931908414225</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2371021278781488</v>
+        <v>0.1358426894004492</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.874894879453305</v>
+        <v>1.721350773291588</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09792663180010021</v>
+        <v>0.05610500903850858</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.833397458235803</v>
+        <v>1.697575696484745</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1220076893054998</v>
+        <v>0.0699015362344145</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.305762781659078</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.979503623249646</v>
+        <v>1.78128415854588</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07346497957632797</v>
+        <v>0.04209034475244181</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.004342117273686</v>
+        <v>1.795514895185738</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05585313394007747</v>
+        <v>0.03199997708567626</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.305762781659078</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.042552013093021</v>
+        <v>1.817406518885433</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02470398649499714</v>
+        <v>0.01415241372002731</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.036057590715974</v>
+        <v>1.813685200940802</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01960153860508638</v>
+        <v>0.0112289314162322</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.050550307793771</v>
+        <v>1.82198750641572</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009718253783466718</v>
+        <v>0.005565796546380339</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.050371751089294</v>
+        <v>1.821883060766997</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005650486249503828</v>
+        <v>0.003235849630631309</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.051946831408553</v>
+        <v>1.822783518316202</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002822743124751914</v>
+        <v>0.001615424815315654</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.051938310677476</v>
+        <v>1.82277650077792</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001392079006917507</v>
+        <v>0.0007941521891421133</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.051897945025743</v>
+        <v>1.822751236448882</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008060496250303649</v>
+        <v>0.0004589337361284804</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.05211723034811</v>
+        <v>1.822874994906104</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002650683837906009</v>
+        <v>0.0001512379079780336</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.051842886828066</v>
+        <v>1.82271481676042</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001319932599835336</v>
+        <v>7.360269015448652e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.051839402688656</v>
+        <v>1.822710686516496</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.838588390325518e-05</v>
+        <v>3.658533421184461e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.05184655010353</v>
+        <v>1.822712656998087</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.055270670444892e-05</v>
+        <v>1.633162402266935e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.051839146167925</v>
+        <v>1.822706260300931</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.051842751877116</v>
+        <v>1.822706102823427</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.051835082156022</v>
+        <v>1.822699435859556</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.051831596935714</v>
+        <v>1.82269557378446</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.051827049623529</v>
+        <v>1.822691026472275</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.051827139568179</v>
+        <v>1.822691116416925</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.051826281634594</v>
+        <v>1.82269025848334</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.051826509955628</v>
+        <v>1.822690486804375</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.051825714291417</v>
+        <v>1.822689691140163</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.051825776560789</v>
+        <v>1.822689753409536</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.051825804236067</v>
+        <v>1.822689781084813</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.051825956450089</v>
+        <v>1.822689933298836</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.051825610509128</v>
+        <v>1.822689587357875</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.05182568661614</v>
+        <v>1.822689663464886</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.051825852667801</v>
+        <v>1.822689829516548</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.051826212446401</v>
+        <v>1.822690189295147</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.051826233202859</v>
+        <v>1.822690210051606</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.051826336985147</v>
+        <v>1.822690313833894</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.051826565306182</v>
+        <v>1.822690542154929</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.051826440767436</v>
+        <v>1.822690417616182</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.051826468442713</v>
+        <v>1.82269044529146</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.051826523793267</v>
+        <v>1.822690500642013</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.051826786708397</v>
+        <v>1.822690763557144</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.051826703682567</v>
+        <v>1.822690680531313</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.05182649611799</v>
+        <v>1.822690472966736</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.051826509955628</v>
+        <v>1.822690486804375</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.051826648332013</v>
+        <v>1.82269062518076</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.051826364660424</v>
+        <v>1.822690341509171</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.051826191689944</v>
+        <v>1.82269016853869</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.051826087907655</v>
+        <v>1.822690064756402</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.051826233202859</v>
+        <v>1.822690210051606</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.051826475361532</v>
+        <v>1.822690452210279</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.051826302391051</v>
+        <v>1.822690279239798</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.051826004881824</v>
+        <v>1.822689981730571</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.051825991044185</v>
+        <v>1.822689967892932</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.051825624346766</v>
+        <v>1.822689601195513</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.051825624346766</v>
+        <v>1.822689601195513</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.051825562077393</v>
+        <v>1.82268953892614</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.051825458295105</v>
+        <v>1.822689435143851</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.051825285324624</v>
+        <v>1.82268926217337</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.051825333756359</v>
+        <v>1.822689310605105</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.051824973977759</v>
+        <v>1.822688950826505</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.051824932464843</v>
+        <v>1.82268890931359</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.051824987815397</v>
+        <v>1.822688964664144</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.051825043165951</v>
+        <v>1.822689020014698</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.051825084678867</v>
+        <v>1.822689061527613</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.051824814844916</v>
+        <v>1.822688791693663</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.05182487019547</v>
+        <v>1.822688847044216</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.051825015490674</v>
+        <v>1.82268899233942</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.051824980896578</v>
+        <v>1.822688957745324</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.051824967058939</v>
+        <v>1.822688943907686</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.051825057003589</v>
+        <v>1.822689033852336</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.051825375269274</v>
+        <v>1.82268935211802</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.051825195379974</v>
+        <v>1.82268917222872</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.051825236892889</v>
+        <v>1.822689213741636</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.05182505008477</v>
+        <v>1.822689026933517</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.051825119272962</v>
+        <v>1.822689096121709</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.051824918627205</v>
+        <v>1.822688895475951</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.05182496014012</v>
+        <v>1.822688936988867</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.051824987815397</v>
+        <v>1.822688964664144</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000006.xlsx
+++ b/out/MLP-S4_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4101586043834686</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4208633601665497</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.37</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4489716589450836</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.483230322599411</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4326735734939575</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4636121690273285</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.407382071018219</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4834886789321899</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4942245185375214</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4463073909282684</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4193492233753204</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4057228863239288</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4685011208057404</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.427117794752121</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4241905808448792</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4262630045413971</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4579700529575348</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4855814576148987</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5374683141708374</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4829642474651337</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4663268327713013</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4397134184837341</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4495798647403717</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5323304533958435</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4638470113277435</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5540081262588501</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.179279226522314</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6803764700889587</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.946808764566225</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5602198839187622</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5011419057846069</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.946808764566225</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.519481360912323</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.179279226522314</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4553188681602478</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4199334681034088</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4538071155548096</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5814495086669922</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5025767683982849</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4978883564472198</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.179279226522314</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5311484336853027</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2117496884784028</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4597792327404022</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2117496884784028</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4855711162090302</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2117496884784028</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.532697856426239</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.179279226522314</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.573639988899231</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6030703783035278</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6988514065742493</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.946808764566225</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003234725534667959</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4163341631488183</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6497135758399963</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.179279226522314</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8334566526871295</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09614876815877423</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4928768873214722</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3198619224365773</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5469874143600464</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3198619224365773</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5451148748397827</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3196210123567867</v>
+        <v>0.1805492523242068</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7401277043068341</v>
+        <v>0.1854226701566546</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4563125967979431</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.801350513402749</v>
+        <v>0.5517641376967581</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1416150967164862</v>
+        <v>0.0354786007527919</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5646481513977051</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.343372730344206</v>
+        <v>0.4370277559345695</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2480522724041377</v>
+        <v>0.06214413394122734</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5435370206832886</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.697931908414225</v>
+        <v>0.5258548144014841</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1358426894004492</v>
+        <v>0.03403238920826912</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5389155149459839</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.721350773291588</v>
+        <v>0.5317218943881942</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.05610500903850858</v>
+        <v>0.01405587236647913</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4696550369262695</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.697575696484745</v>
+        <v>0.5257655733604077</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0699015362344145</v>
+        <v>0.01751192035485199</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6650652289390564</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2117496884784028</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.78128415854588</v>
+        <v>0.5467368825751256</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04209034475244181</v>
+        <v>0.01054288952356224</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4770792126655579</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.795514895185738</v>
+        <v>0.5503006069246938</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03199997708567626</v>
+        <v>0.008015056170379379</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.7210294604301453</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.817406518885433</v>
+        <v>0.5557830431526014</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01415241372002731</v>
+        <v>0.003542299890334637</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3357082605361938</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.813685200940802</v>
+        <v>0.5548469297300284</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0112289314162322</v>
+        <v>0.002809788383591186</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.2803340554237366</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.82198750641572</v>
+        <v>0.5569231848985744</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005565796546380339</v>
+        <v>0.001390825986924216</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.8351554870605469</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.821883060766997</v>
+        <v>0.5568932728689899</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003235849630631309</v>
+        <v>0.0008066670080306419</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7869539260864258</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.946808764566225</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.822783518316202</v>
+        <v>0.5571150436555501</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001615424815315654</v>
+        <v>0.0003993789036425062</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5036765336990356</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.946808764566225</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.82277650077792</v>
+        <v>0.5571095401765174</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0007941521891421133</v>
+        <v>0.0001962253713667192</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.504249095916748</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.946808764566225</v>
+        <v>0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.822751236448882</v>
+        <v>0.5570994463583666</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004589337361284804</v>
+        <v>0.0001118178472265958</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5552533864974976</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.822874994906104</v>
+        <v>0.5571267508286664</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001512379079780336</v>
+        <v>3.294349193752244e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3054096400737762</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.82271481676042</v>
+        <v>0.5570829576964944</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.360269015448652e-05</v>
+        <v>1.521212032543939e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3335810899734497</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.822710686516496</v>
+        <v>0.5570781813480568</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.658533421184461e-05</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3151627480983734</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.822712656998087</v>
+        <v>0.5570749748963635</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.3672105371952057</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.822706260300931</v>
+        <v>0.5570695884122059</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4395387172698975</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.822706102823427</v>
+        <v>0.557066203793755</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3760620951652527</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.822699435859556</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4232266545295715</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.82269557378446</v>
+        <v>0.5570609168985391</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3693590760231018</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.822691026472275</v>
+        <v>0.5570611452195737</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.323373943567276</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.822691116416925</v>
+        <v>0.5570612351642237</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2558172047138214</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.82269025848334</v>
+        <v>0.5570603772306388</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3794255256652832</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.822690486804375</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.323762446641922</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.822689691140163</v>
+        <v>0.5570598098874618</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2438666820526123</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.822689753409536</v>
+        <v>0.5570598721568349</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3000129163265228</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.822689781084813</v>
+        <v>0.5570598998321118</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3639110922813416</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.822689933298836</v>
+        <v>0.5570600520461351</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2989999353885651</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.822689587357875</v>
+        <v>0.5570597061051733</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3089846074581146</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.822689663464886</v>
+        <v>0.557059782212185</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2811148762702942</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.822689829516548</v>
+        <v>0.5570599482638465</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4430820345878601</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.822690189295147</v>
+        <v>0.5570603080424467</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4821337163448334</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.822690210051606</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4448250532150269</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.822690313833894</v>
+        <v>0.5570604325811929</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3540030121803284</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.822690542154929</v>
+        <v>0.5570606609022275</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3226549327373505</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.822690417616182</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.259161114692688</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.82269044529146</v>
+        <v>0.5570605640387581</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.413427323102951</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.822690500642013</v>
+        <v>0.5570606193893121</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3308017551898956</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.822690763557144</v>
+        <v>0.5570608823044428</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3776414692401886</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.822690680531313</v>
+        <v>0.557060799278612</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3048703968524933</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.822690472966736</v>
+        <v>0.5570605917140352</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.293840080499649</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.822690486804375</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3408029973506927</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.82269062518076</v>
+        <v>0.5570607439280583</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3459952771663666</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.822690341509171</v>
+        <v>0.5570604602564697</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2918729484081268</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.82269016853869</v>
+        <v>0.5570602872859889</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3833199739456177</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.822690064756402</v>
+        <v>0.5570601835037005</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3972610533237457</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.822690210051606</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3701797127723694</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.822690452210279</v>
+        <v>0.5570605709575775</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3356543481349945</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.822690279239798</v>
+        <v>0.5570603979870966</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3043469190597534</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.822689981730571</v>
+        <v>0.5570601004778696</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3197482824325562</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.822689967892932</v>
+        <v>0.5570600866402311</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3052237927913666</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.822689601195513</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3461170494556427</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.822689601195513</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3870570957660675</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.82268953892614</v>
+        <v>0.5570596576734388</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.327826201915741</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.822689435143851</v>
+        <v>0.5570595538911502</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3286643624305725</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.82268926217337</v>
+        <v>0.5570593809206695</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3325860202312469</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.822689310605105</v>
+        <v>0.557059429352404</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3117787837982178</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.822688950826505</v>
+        <v>0.557059069573804</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.2828027904033661</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.82268890931359</v>
+        <v>0.5570590280608886</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3278931677341461</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.822688964664144</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2926397323608398</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.822689020014698</v>
+        <v>0.5570591387619963</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3038170337677002</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.822689061527613</v>
+        <v>0.5570591802749116</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3017835021018982</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.822688791693663</v>
+        <v>0.5570589104409616</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3453263342380524</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.822688847044216</v>
+        <v>0.5570589657915156</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3121210932731628</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.82268899233942</v>
+        <v>0.5570591110867195</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3306806981563568</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.822688957745324</v>
+        <v>0.5570590764926232</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3012828230857849</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.822688943907686</v>
+        <v>0.5570590626549846</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4011834859848022</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.822689033852336</v>
+        <v>0.5570591525996348</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5582238435745239</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.82268935211802</v>
+        <v>0.5570594708653195</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3879176378250122</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.82268917222872</v>
+        <v>0.5570592909760194</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.362711101770401</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.822689213741636</v>
+        <v>0.5570593324889347</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3789815604686737</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.822689026933517</v>
+        <v>0.5570591456808155</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3237778544425964</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.822689096121709</v>
+        <v>0.5570592148690079</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3340566754341125</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.822688895475951</v>
+        <v>0.5570590142232501</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3145454525947571</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.72</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.822688936988867</v>
+        <v>0.5570590557361655</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3517282009124756</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.822688964664144</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
   </sheetData>
